--- a/artfynd/A 13760-2026 artfynd.xlsx
+++ b/artfynd/A 13760-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107202523</v>
+        <v>130021384</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ekebergsflon, Jmt</t>
+          <t>Almåsaberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453210.5398523134</v>
+        <v>452906</v>
       </c>
       <c r="R2" t="n">
-        <v>7043792.04146984</v>
+        <v>7044060</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-03-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-03-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,15 +765,123 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>107202523</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ekebergsflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>453210</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7043792</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-03-09</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-03-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Magnus Adolfsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Magnus Adolfsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13760-2026 artfynd.xlsx
+++ b/artfynd/A 13760-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021384</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,8 +892,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107202523</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>